--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,36 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Установка кабель каналов в офисе</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Евроком ООО</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Пятигорск</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46284.52924768518</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SMT-в00011000266</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Администрация Пятигорск</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Необходимо закупить футболки и шорты в колличестве 8 штук</t>
         </is>
       </c>
     </row>

--- a/Заявки_без_координат.xlsx
+++ b/Заявки_без_координат.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,36 +480,6 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Установка кабель каналов в офисе</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Евроком ООО</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Пятигорск</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46284.52924768518</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SMT-в00011000266</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Администрация Пятигорск</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Необходимо закупить футболки и шорты в колличестве 8 штук</t>
         </is>
       </c>
     </row>
